--- a/Result/DivideRBM_RQAE_eps0=2^-10_R=12_maxdeg=5_integEpsabs=1e-4.xlsx
+++ b/Result/DivideRBM_RQAE_eps0=2^-10_R=12_maxdeg=5_integEpsabs=1e-4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koich\Desktop\Code\DivQCOSDE\Result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446A92EA-9F77-443D-924A-2300E0EF4375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBA0FB6-E59A-4B3E-8369-1473365C3B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1890" yWindow="1185" windowWidth="18390" windowHeight="9015" xr2:uid="{DDFBC754-980A-4BFD-AE2C-311ED991EAD0}"/>
+    <workbookView xWindow="1215" yWindow="1215" windowWidth="18390" windowHeight="9015" xr2:uid="{DDFBC754-980A-4BFD-AE2C-311ED991EAD0}"/>
   </bookViews>
   <sheets>
     <sheet name="RQAE_eps0=2^-10_R=12_deg10" sheetId="1" r:id="rId1"/>
@@ -982,25 +982,25 @@
                 <c:formatCode>#,##0_);[Red]\(#,##0\)</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>23854685.785251372</c:v>
+                  <c:v>11380920.678261478</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>32800192.954720639</c:v>
+                  <c:v>15648765.932609532</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>47709371.570502743</c:v>
+                  <c:v>22761841.356522955</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>65600385.909441277</c:v>
+                  <c:v>31297531.865219064</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>95418743.141005486</c:v>
+                  <c:v>45523682.71304591</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>134182607.54203898</c:v>
+                  <c:v>64017678.815220803</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>190837486.28201097</c:v>
+                  <c:v>91047365.42609182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3169,7 +3169,7 @@
         <v>8</v>
       </c>
       <c r="K2" s="2">
-        <f t="shared" ref="K2:K9" si="0">AVERAGEIF($A$2:$A$1048576,$J2,$E$2:$E$1048576)</f>
+        <f t="shared" ref="K2:K8" si="0">AVERAGEIF($A$2:$A$1048576,$J2,$E$2:$E$1048576)</f>
         <v>2.28445621836448E-4</v>
       </c>
       <c r="L2" s="5">
@@ -3177,20 +3177,20 @@
         <v>2.6182040333317297E-4</v>
       </c>
       <c r="M2" s="3">
-        <f t="shared" ref="M2:M9" si="1">AVERAGEIF($A$2:$A$1048576,$J2,$G$2:$G$1048576)</f>
+        <f t="shared" ref="M2:M8" si="1">AVERAGEIF($A$2:$A$1048576,$J2,$G$2:$G$1048576)</f>
         <v>2653617.4</v>
       </c>
       <c r="N2" s="4">
-        <f t="shared" ref="N2:N9" si="2">AVERAGEIF($A$2:$A$1048576,$J2,$H$2:$H$1048576)</f>
+        <f t="shared" ref="N2:N8" si="2">AVERAGEIF($A$2:$A$1048576,$J2,$H$2:$H$1048576)</f>
         <v>2894.9</v>
       </c>
       <c r="Q2" s="3">
-        <f t="shared" ref="Q2:Q9" si="3">$J2/$L2/$L2*SQRT($B$2*(1-$B$2))</f>
-        <v>55678395.031124085</v>
+        <f t="shared" ref="Q2:Q8" si="3">$J2/$L2/$L2*$B$2*(1-$B$2)</f>
+        <v>26563812.369891327</v>
       </c>
       <c r="R2" s="3">
-        <f t="shared" ref="R2:R8" si="4">$J2/(0.0004^2)*SQRT($B$2*(1-$B$2))</f>
-        <v>23854685.785251372</v>
+        <f t="shared" ref="R2:R8" si="4">$J2/(0.0004^2)*$B$2*(1-$B$2)</f>
+        <v>11380920.678261478</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -3240,11 +3240,11 @@
       </c>
       <c r="Q3" s="3">
         <f t="shared" si="3"/>
-        <v>155563992.38196081</v>
+        <v>74218603.155418262</v>
       </c>
       <c r="R3" s="3">
         <f t="shared" si="4"/>
-        <v>32800192.954720639</v>
+        <v>15648765.932609532</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
@@ -3294,11 +3294,11 @@
       </c>
       <c r="Q4" s="3">
         <f t="shared" si="3"/>
-        <v>204316798.559778</v>
+        <v>97478260.605840072</v>
       </c>
       <c r="R4" s="3">
         <f t="shared" si="4"/>
-        <v>47709371.570502743</v>
+        <v>22761841.356522955</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -3348,11 +3348,11 @@
       </c>
       <c r="Q5" s="3">
         <f t="shared" si="3"/>
-        <v>97416192.321062639</v>
+        <v>46476653.164291337</v>
       </c>
       <c r="R5" s="3">
         <f t="shared" si="4"/>
-        <v>65600385.909441277</v>
+        <v>31297531.865219064</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
@@ -3402,11 +3402,11 @@
       </c>
       <c r="Q6" s="3">
         <f t="shared" si="3"/>
-        <v>147983150.57908934</v>
+        <v>70601831.171514302</v>
       </c>
       <c r="R6" s="3">
         <f t="shared" si="4"/>
-        <v>95418743.141005486</v>
+        <v>45523682.71304591</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.4">
@@ -3456,11 +3456,11 @@
       </c>
       <c r="Q7" s="3">
         <f t="shared" si="3"/>
-        <v>502791458.49127215</v>
+        <v>239878645.15635109</v>
       </c>
       <c r="R7" s="3">
         <f t="shared" si="4"/>
-        <v>134182607.54203898</v>
+        <v>64017678.815220803</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.4">
@@ -3510,11 +3510,11 @@
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="3"/>
-        <v>192650911.33361959</v>
+        <v>91912539.122116357</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="4"/>
-        <v>190837486.28201097</v>
+        <v>91047365.42609182</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
@@ -5112,7 +5112,7 @@
         <v>8.0439987184433001E-5</v>
       </c>
       <c r="F67" s="1">
-        <f t="shared" ref="F67:F74" si="7">E67*E67</f>
+        <f t="shared" ref="F67:F71" si="7">E67*E67</f>
         <v>6.4705915382317454E-9</v>
       </c>
       <c r="G67">

--- a/Result/DivideRBM_RQAE_eps0=2^-10_R=12_maxdeg=5_integEpsabs=1e-4.xlsx
+++ b/Result/DivideRBM_RQAE_eps0=2^-10_R=12_maxdeg=5_integEpsabs=1e-4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koich\Desktop\Code\DivQCOSDE\Result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBA0FB6-E59A-4B3E-8369-1473365C3B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7329BAD6-2DED-4D66-9A57-495CD977849F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1215" yWindow="1215" windowWidth="18390" windowHeight="9015" xr2:uid="{DDFBC754-980A-4BFD-AE2C-311ED991EAD0}"/>
+    <workbookView xWindow="345" yWindow="1635" windowWidth="18390" windowHeight="9015" xr2:uid="{DDFBC754-980A-4BFD-AE2C-311ED991EAD0}"/>
   </bookViews>
   <sheets>
     <sheet name="RQAE_eps0=2^-10_R=12_deg10" sheetId="1" r:id="rId1"/>
@@ -111,9 +111,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.00000"/>
     <numFmt numFmtId="177" formatCode="0.000000"/>
+    <numFmt numFmtId="178" formatCode="#,##0.0000;[Red]\-#,##0.0000"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -704,7 +705,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -721,6 +722,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3292,6 +3296,8 @@
         <f t="shared" si="2"/>
         <v>4094</v>
       </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
       <c r="Q4" s="3">
         <f t="shared" si="3"/>
         <v>97478260.605840072</v>
@@ -3346,6 +3352,8 @@
         <f t="shared" si="2"/>
         <v>4801.8</v>
       </c>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
       <c r="Q5" s="3">
         <f t="shared" si="3"/>
         <v>46476653.164291337</v>
@@ -3400,6 +3408,8 @@
         <f t="shared" si="2"/>
         <v>5792</v>
       </c>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
       <c r="Q6" s="3">
         <f t="shared" si="3"/>
         <v>70601831.171514302</v>
@@ -3454,6 +3464,8 @@
         <f t="shared" si="2"/>
         <v>6867.9</v>
       </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
       <c r="Q7" s="3">
         <f t="shared" si="3"/>
         <v>239878645.15635109</v>
@@ -3508,6 +3520,8 @@
         <f t="shared" si="2"/>
         <v>8190.3</v>
       </c>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
       <c r="Q8" s="3">
         <f t="shared" si="3"/>
         <v>91912539.122116357</v>
